--- a/data/trans_orig/IP07_C14_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07_C14_2023-Clase-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si se han producido situaciones de cyberbulling en su colegio en 2023 (tasa de respuesta: 94,11%)</t>
+          <t>Menores según si se han producido situaciones de cyberbulling en su colegio/instituto en 2023 (tasa de respuesta: 94,11%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4654</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1778</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8296</t>
+          <t>9357</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2266</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9096</t>
+          <t>9148</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9509</t>
+          <t>9354</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5725</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15418</t>
+          <t>15252</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>30125</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>25252</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>32832</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>87,04%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>72,96%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>94,86%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>24630</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>20988</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>27506</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>84,11%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>71,67%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>93,93%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28825</t>
+          <t>25806</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24583</t>
+          <t>21528</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31565</t>
+          <t>28410</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>53454</t>
+          <t>55931</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47545</t>
+          <t>50033</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57238</t>
+          <t>60208</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>92,22%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>34609</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>34609</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>34609</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>29284</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>29284</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>29284</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>33679</t>
+          <t>30676</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33679</t>
+          <t>30676</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33679</t>
+          <t>30676</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>62963</t>
+          <t>65285</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>62963</t>
+          <t>65285</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>62963</t>
+          <t>65285</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,74 +1063,74 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4685</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1577</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9207</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>15,24%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,13%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>29,95%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2117</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5220</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7,43%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>18,31%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4832</t>
+          <t>2139</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>573</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9622</t>
+          <t>4857</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
           <t>16,12%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>32,09%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>6949</t>
+          <t>6824</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3553</t>
+          <t>3358</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12028</t>
+          <t>11839</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>26051</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>21529</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>29159</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>84,76%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>70,05%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,87%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>26383</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>23280</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>27878</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>92,57%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>81,69%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,82%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>25149</t>
+          <t>27998</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20359</t>
+          <t>25280</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27941</t>
+          <t>29564</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
+          <t>92,9%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
           <t>83,88%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>67,91%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>51533</t>
+          <t>54049</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>46454</t>
+          <t>49034</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>54929</t>
+          <t>57515</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,48%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>30736</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>30736</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>30736</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>28500</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>28500</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>28500</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29981</t>
+          <t>30137</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29981</t>
+          <t>30137</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29981</t>
+          <t>30137</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>58482</t>
+          <t>60873</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>58482</t>
+          <t>60873</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>58482</t>
+          <t>60873</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2484</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6842</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,43%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>25,97%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3547</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,55%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3316</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>6,6%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>25,1%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2558</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7222</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,47%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>3487</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>1414</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8749</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>19,85%</t>
         </is>
       </c>
     </row>
@@ -1519,74 +1519,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>19508</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>25812</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>90,57%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>74,03%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,96%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>13062</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>10581</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>14128</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>92,45%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>74,9%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>14197</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>11884</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>15200</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>93,4%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>78,18%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>24448</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>19784</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>26484</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>90,53%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>73,26%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,07%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>47</t>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>37510</t>
+          <t>38064</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>32385</t>
+          <t>33302</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>39768</t>
+          <t>40137</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>26350</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>26350</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>26350</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>14128</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>14128</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>14128</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>27006</t>
+          <t>15200</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27006</t>
+          <t>15200</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27006</t>
+          <t>15200</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>41134</t>
+          <t>41551</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>41134</t>
+          <t>41551</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>41134</t>
+          <t>41551</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8359</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4047</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>15616</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13,25%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6,42%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>24,76%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>9220</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2159</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>18446</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>14,03%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,29%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>28,07%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8931</t>
+          <t>9415</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4427</t>
+          <t>5614</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15806</t>
+          <t>15440</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>18151</t>
+          <t>17774</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8354</t>
+          <t>11354</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27149</t>
+          <t>25805</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>54714</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>47457</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>59026</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>86,75%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>75,24%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>93,58%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>56483</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>47257</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>63544</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>85,97%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>71,93%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,71%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>55767</t>
+          <t>32718</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48892</t>
+          <t>26693</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>60271</t>
+          <t>36519</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>112250</t>
+          <t>87432</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>103252</t>
+          <t>79401</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>122047</t>
+          <t>93852</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>89,21%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>63073</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>63073</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>63073</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>65703</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>65703</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>65703</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>64698</t>
+          <t>42133</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>64698</t>
+          <t>42133</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>64698</t>
+          <t>42133</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>130401</t>
+          <t>105206</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>130401</t>
+          <t>105206</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>130401</t>
+          <t>105206</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5952</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2326</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>12764</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>10,39%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>22,27%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>4560</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1972</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8738</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>13,93%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>26,69%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2498</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13105</t>
+          <t>9064</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>10757</t>
+          <t>10882</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5422</t>
+          <t>6181</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18049</t>
+          <t>17700</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,03%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>51356</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>44544</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>54982</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>89,61%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>77,73%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>95,94%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>28177</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>23999</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>30765</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>86,07%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>73,31%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>93,98%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>52819</t>
+          <t>30788</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45911</t>
+          <t>26654</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56518</t>
+          <t>33393</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>80996</t>
+          <t>82144</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>73704</t>
+          <t>75326</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>86331</t>
+          <t>86845</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,36%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>57308</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>57308</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>57308</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>32737</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>32737</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>32737</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>59016</t>
+          <t>35718</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>59016</t>
+          <t>35718</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>59016</t>
+          <t>35718</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>91753</t>
+          <t>93026</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>91753</t>
+          <t>93026</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>91753</t>
+          <t>93026</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,62 +2435,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>4005</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1376</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>8433</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>12,14%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>4,17%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>25,55%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>4191</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1920</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>8698</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>14,78%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>6,77%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>30,68%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>4168</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1698</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8318</t>
+          <t>8868</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>8530</t>
+          <t>8173</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4485</t>
+          <t>4433</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13505</t>
+          <t>13450</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>20,97%</t>
         </is>
       </c>
     </row>
@@ -2548,67 +2548,67 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>29002</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>24574</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>31631</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>87,86%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>74,45%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>95,83%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>24157</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>19650</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>26428</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>85,22%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>69,32%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>93,23%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>28158</t>
+          <t>26977</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24179</t>
+          <t>22277</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30799</t>
+          <t>29515</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>52315</t>
+          <t>55979</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>47340</t>
+          <t>50702</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>56360</t>
+          <t>59719</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>93,09%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>28348</t>
+          <t>33007</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>28348</t>
+          <t>33007</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>28348</t>
+          <t>33007</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>32497</t>
+          <t>31145</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>32497</t>
+          <t>31145</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>32497</t>
+          <t>31145</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>60845</t>
+          <t>64152</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>60845</t>
+          <t>64152</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>60845</t>
+          <t>64152</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>29969</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>20790</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>39963</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>12,23%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>8,48%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>16,31%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>25810</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>15131</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>35122</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>12,99%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>7,61%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>17,68%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>31710</t>
+          <t>26524</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23480</t>
+          <t>19477</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43695</t>
+          <t>35312</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>57520</t>
+          <t>56493</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>43686</t>
+          <t>44556</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>71182</t>
+          <t>69377</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>215113</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>205119</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>224292</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>87,77%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>83,69%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>91,52%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>172891</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>163579</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>183570</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>87,01%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>82,32%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>92,39%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>215167</t>
+          <t>158486</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>203182</t>
+          <t>149698</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>223397</t>
+          <t>165533</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>388058</t>
+          <t>373600</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>374396</t>
+          <t>360716</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>401892</t>
+          <t>385537</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>89,64%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>245082</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>245082</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>245082</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>198701</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>198701</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>198701</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>246877</t>
+          <t>185010</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>246877</t>
+          <t>185010</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>246877</t>
+          <t>185010</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>445578</t>
+          <t>430093</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>445578</t>
+          <t>430093</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>445578</t>
+          <t>430093</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
